--- a/entregables/QUINIELA_2026_JAVIER_FINAL.xlsx
+++ b/entregables/QUINIELA_2026_JAVIER_FINAL.xlsx
@@ -382,22 +382,145 @@
     <t xml:space="preserve">Dieciseisavos</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filadelfia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_DEIJL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_AEHIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Francisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_EHIJK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad de México</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_CEFHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2J</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Ángeles</t>
-  </si>
-  <si>
     <t xml:space="preserve">2A</t>
   </si>
   <si>
     <t xml:space="preserve">2B</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston</t>
+    <t xml:space="preserve">Monterrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vancouver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_EFGIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva York</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_CDFGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seattle</t>
   </si>
   <si>
     <t xml:space="preserve">1E</t>
@@ -406,67 +529,7 @@
     <t xml:space="preserve">3_ABCDF</t>
   </si>
   <si>
-    <t xml:space="preserve">Monterrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva York</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_CDFGH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Francisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciudad de México</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_CEFHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atlanta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seattle</t>
+    <t xml:space="preserve">Kansas City</t>
   </si>
   <si>
     <t xml:space="preserve">1D</t>
@@ -475,165 +538,102 @@
     <t xml:space="preserve">3_BEFIJ</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_AEHIJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vancouver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_EFGIJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_EHIJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kansas City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2H</t>
+    <t xml:space="preserve">Octavos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuartos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W90</t>
   </si>
   <si>
     <t xml:space="preserve">Miami</t>
   </si>
   <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filadelfia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_DEIJL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octavos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuartos</t>
+    <t xml:space="preserve">W91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W92</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-09</t>
   </si>
   <si>
-    <t xml:space="preserve">W89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W90</t>
+    <t xml:space="preserve">W93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W94</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">W93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W92</t>
-  </si>
-  <si>
     <t xml:space="preserve">W95</t>
   </si>
   <si>
@@ -643,16 +643,16 @@
     <t xml:space="preserve">Semifinal</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W98</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
     <t xml:space="preserve">W99</t>
@@ -5461,18 +5461,18 @@
         <v>121</v>
       </c>
       <c r="F5" s="0" t="str">
-        <f aca="false">Grupos!$R$7</f>
-        <v>Corea del Sur</v>
+        <f aca="false">Grupos!$R$87</f>
+        <v>Argentina</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0" t="str">
-        <f aca="false">Grupos!$R$16</f>
-        <v>Suiza</v>
+        <f aca="false">Grupos!$R$70</f>
+        <v>Uruguay</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>122</v>
@@ -5495,17 +5495,18 @@
         <v>125</v>
       </c>
       <c r="F6" s="0" t="str">
-        <f aca="false">Grupos!$R$42</f>
-        <v>Alemania</v>
+        <f aca="false">Grupos!$R$34</f>
+        <v>Australia</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="I6" s="0" t="str">
+        <f aca="false">Grupos!$R$61</f>
+        <v>Irán</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>126</v>
@@ -5528,18 +5529,17 @@
         <v>128</v>
       </c>
       <c r="F7" s="0" t="str">
-        <f aca="false">Grupos!$R$51</f>
-        <v>Holanda</v>
+        <f aca="false">Grupos!$R$96</f>
+        <v>Portugal</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="0" t="str">
-        <f aca="false">Grupos!$R$25</f>
-        <v>Marruecos</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>129</v>
@@ -5553,30 +5553,29 @@
         <v>118</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F8" s="0" t="str">
-        <f aca="false">Grupos!$R$24</f>
-        <v>Brasil</v>
+        <f aca="false">Grupos!$R$60</f>
+        <v>Bélgica</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="str">
-        <f aca="false">Grupos!$R$52</f>
-        <v>Japón</v>
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5587,7 +5586,7 @@
         <v>118</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>134</v>
@@ -5596,17 +5595,18 @@
         <v>135</v>
       </c>
       <c r="F9" s="0" t="str">
-        <f aca="false">Grupos!$R$78</f>
-        <v>Francia</v>
+        <f aca="false">Grupos!$R$24</f>
+        <v>Brasil</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>61</v>
+      <c r="I9" s="0" t="str">
+        <f aca="false">Grupos!$R$52</f>
+        <v>Japón</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>136</v>
@@ -5620,13 +5620,13 @@
         <v>118</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F10" s="0" t="str">
         <f aca="false">Grupos!$R$43</f>
@@ -5643,7 +5643,7 @@
         <v>Noruega</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5654,17 +5654,17 @@
         <v>118</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F11" s="0" t="str">
-        <f aca="false">Grupos!$R$6</f>
-        <v>México</v>
+        <f aca="false">Grupos!$R$105</f>
+        <v>Inglaterra</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>2</v>
@@ -5673,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,7 +5687,7 @@
         <v>118</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>144</v>
@@ -5696,18 +5696,17 @@
         <v>145</v>
       </c>
       <c r="F12" s="0" t="str">
-        <f aca="false">Grupos!$R$97</f>
-        <v>Colombia</v>
+        <f aca="false">Grupos!$R$6</f>
+        <v>México</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="0" t="str">
-        <f aca="false">Grupos!$R$106</f>
-        <v>Croacia</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>146</v>
@@ -5721,29 +5720,30 @@
         <v>118</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D13" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="F13" s="0" t="str">
+        <f aca="false">Grupos!$R$69</f>
+        <v>España</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="str">
+        <f aca="false">Grupos!$R$88</f>
+        <v>Argelia</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="F13" s="0" t="str">
-        <f aca="false">Grupos!$R$33</f>
-        <v>Estados Unidos</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5754,29 +5754,30 @@
         <v>118</v>
       </c>
       <c r="C14" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="F14" s="0" t="str">
+        <f aca="false">Grupos!$R$7</f>
+        <v>Corea del Sur</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="0" t="str">
+        <f aca="false">Grupos!$R$16</f>
+        <v>Suiza</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="F14" s="0" t="str">
-        <f aca="false">Grupos!$R$60</f>
-        <v>Bélgica</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5787,29 +5788,30 @@
         <v>118</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="D15" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="0" t="str">
+        <f aca="false">Grupos!$R$51</f>
+        <v>Holanda</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="0" t="str">
+        <f aca="false">Grupos!$R$25</f>
+        <v>Marruecos</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="F15" s="0" t="str">
-        <f aca="false">Grupos!$R$15</f>
-        <v>Canadá</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5820,29 +5822,29 @@
         <v>118</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="E16" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="0" t="str">
+        <f aca="false">Grupos!$R$15</f>
+        <v>Canadá</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="F16" s="0" t="str">
-        <f aca="false">Grupos!$R$105</f>
-        <v>Inglaterra</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5853,30 +5855,29 @@
         <v>118</v>
       </c>
       <c r="C17" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="F17" s="0" t="str">
+        <f aca="false">Grupos!$R$78</f>
+        <v>Francia</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="0" t="str">
-        <f aca="false">Grupos!$R$87</f>
-        <v>Argentina</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="0" t="str">
-        <f aca="false">Grupos!$R$70</f>
-        <v>Uruguay</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5887,30 +5888,30 @@
         <v>118</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D18" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="F18" s="0" t="str">
+        <f aca="false">Grupos!$R$97</f>
+        <v>Colombia</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="0" t="str">
+        <f aca="false">Grupos!$R$106</f>
+        <v>Croacia</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="F18" s="0" t="str">
-        <f aca="false">Grupos!$R$69</f>
-        <v>España</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="0" t="str">
-        <f aca="false">Grupos!$R$88</f>
-        <v>Argelia</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,29 +5922,29 @@
         <v>118</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D19" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="F19" s="0" t="str">
+        <f aca="false">Grupos!$R$42</f>
+        <v>Alemania</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="F19" s="0" t="str">
-        <f aca="false">Grupos!$R$96</f>
-        <v>Portugal</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5954,30 +5955,29 @@
         <v>118</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="D20" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="0" t="str">
+        <f aca="false">Grupos!$R$33</f>
+        <v>Estados Unidos</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="F20" s="0" t="str">
-        <f aca="false">Grupos!$R$34</f>
-        <v>Australia</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="0" t="str">
-        <f aca="false">Grupos!$R$61</f>
-        <v>Irán</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5985,33 +5985,33 @@
         <v>89</v>
       </c>
       <c r="B21" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="D21" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="F21" s="0" t="str">
+        <f aca="false">IF(G5&gt;H5,F5,I5)</f>
+        <v>Argentina</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="0" t="str">
+        <f aca="false">IF(G6&gt;H6,F6,I6)</f>
+        <v>Irán</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="F21" s="0" t="str">
-        <f aca="false">IF(G6&gt;H6,F6,I6)</f>
-        <v>Alemania</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="0" t="str">
-        <f aca="false">IF(G9&gt;H9,F9,I9)</f>
-        <v>Francia</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,33 +6019,33 @@
         <v>90</v>
       </c>
       <c r="B22" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>173</v>
-      </c>
       <c r="D22" s="0" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E22" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="0" t="str">
+        <f aca="false">IF(G7&gt;H7,F7,I7)</f>
+        <v>Portugal</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0" t="str">
+        <f aca="false">IF(G8&gt;H8,F8,I8)</f>
+        <v>Bélgica</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="F22" s="0" t="str">
-        <f aca="false">IF(G5&gt;H5,F5,I5)</f>
-        <v>Suiza</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="0" t="str">
-        <f aca="false">IF(G7&gt;H7,F7,I7)</f>
-        <v>Holanda</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6053,19 +6053,19 @@
         <v>91</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C23" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>179</v>
-      </c>
       <c r="F23" s="0" t="str">
-        <f aca="false">IF(G8&gt;H8,F8,I8)</f>
+        <f aca="false">IF(G9&gt;H9,F9,I9)</f>
         <v>Brasil</v>
       </c>
       <c r="G23" s="4" t="n">
@@ -6079,7 +6079,7 @@
         <v>Ecuador</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6087,33 +6087,33 @@
         <v>92</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F24" s="0" t="str">
         <f aca="false">IF(G11&gt;H11,F11,I11)</f>
-        <v>México</v>
+        <v>Inglaterra</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="0" t="str">
         <f aca="false">IF(G12&gt;H12,F12,I12)</f>
-        <v>Colombia</v>
+        <v>México</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6121,33 +6121,33 @@
         <v>93</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C25" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="F25" s="0" t="str">
+        <f aca="false">IF(G13&gt;H13,F13,I13)</f>
+        <v>España</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="0" t="str">
+        <f aca="false">IF(G14&gt;H14,F14,I14)</f>
+        <v>Suiza</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="F25" s="0" t="str">
-        <f aca="false">IF(G15&gt;H15,F15,I15)</f>
-        <v>Canadá</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="0" t="str">
-        <f aca="false">IF(G16&gt;H16,F16,I16)</f>
-        <v>Inglaterra</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6155,33 +6155,33 @@
         <v>94</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E26" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="0" t="str">
+        <f aca="false">IF(G15&gt;H15,F15,I15)</f>
+        <v>Holanda</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0" t="str">
+        <f aca="false">IF(G16&gt;H16,F16,I16)</f>
+        <v>Canadá</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="F26" s="0" t="str">
-        <f aca="false">IF(G13&gt;H13,F13,I13)</f>
-        <v>Estados Unidos</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="0" t="str">
-        <f aca="false">IF(G14&gt;H14,F14,I14)</f>
-        <v>Bélgica</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6189,33 +6189,33 @@
         <v>95</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C27" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="F27" s="0" t="str">
+        <f aca="false">IF(G17&gt;H17,F17,I17)</f>
+        <v>Francia</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="0" t="str">
+        <f aca="false">IF(G18&gt;H18,F18,I18)</f>
+        <v>Colombia</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="F27" s="0" t="str">
-        <f aca="false">IF(G18&gt;H18,F18,I18)</f>
-        <v>España</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="0" t="str">
-        <f aca="false">IF(G20&gt;H20,F20,I20)</f>
-        <v>Irán</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6223,33 +6223,33 @@
         <v>96</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E28" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" s="0" t="str">
+        <f aca="false">IF(G19&gt;H19,F19,I19)</f>
+        <v>Alemania</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="0" t="str">
+        <f aca="false">IF(G20&gt;H20,F20,I20)</f>
+        <v>Estados Unidos</v>
+      </c>
+      <c r="J28" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="F28" s="0" t="str">
-        <f aca="false">IF(G17&gt;H17,F17,I17)</f>
-        <v>Argentina</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="0" t="str">
-        <f aca="false">IF(G19&gt;H19,F19,I19)</f>
-        <v>Portugal</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6257,20 +6257,20 @@
         <v>97</v>
       </c>
       <c r="B29" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="D29" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="0" t="s">
         <v>194</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>195</v>
       </c>
       <c r="F29" s="0" t="str">
         <f aca="false">IF(G21&gt;H21,F21,I21)</f>
-        <v>Francia</v>
+        <v>Argentina</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>2</v>
@@ -6280,10 +6280,10 @@
       </c>
       <c r="I29" s="0" t="str">
         <f aca="false">IF(G22&gt;H22,F22,I22)</f>
-        <v>Holanda</v>
+        <v>Portugal</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,33 +6291,33 @@
         <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="D30" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="F30" s="0" t="str">
+        <f aca="false">IF(G23&gt;H23,F23,I23)</f>
+        <v>Brasil</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="0" t="str">
+        <f aca="false">IF(G24&gt;H24,F24,I24)</f>
+        <v>Inglaterra</v>
+      </c>
+      <c r="J30" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="F30" s="0" t="str">
-        <f aca="false">IF(G25&gt;H25,F25,I25)</f>
-        <v>Inglaterra</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="0" t="str">
-        <f aca="false">IF(G26&gt;H26,F26,I26)</f>
-        <v>Estados Unidos</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6325,33 +6325,33 @@
         <v>99</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C31" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="F31" s="0" t="str">
+        <f aca="false">IF(G25&gt;H25,F25,I25)</f>
+        <v>España</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="0" t="str">
+        <f aca="false">IF(G26&gt;H26,F26,I26)</f>
+        <v>Holanda</v>
+      </c>
+      <c r="J31" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="F31" s="0" t="str">
-        <f aca="false">IF(G23&gt;H23,F23,I23)</f>
-        <v>Brasil</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="0" t="str">
-        <f aca="false">IF(G24&gt;H24,F24,I24)</f>
-        <v>Colombia</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6359,20 +6359,20 @@
         <v>100</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>203</v>
       </c>
       <c r="F32" s="0" t="str">
         <f aca="false">IF(G27&gt;H27,F27,I27)</f>
-        <v>España</v>
+        <v>Francia</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>2</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I32" s="0" t="str">
         <f aca="false">IF(G28&gt;H28,F28,I28)</f>
-        <v>Argentina</v>
+        <v>Alemania</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>204</v>
@@ -6399,14 +6399,14 @@
         <v>206</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>207</v>
       </c>
       <c r="F33" s="0" t="str">
         <f aca="false">IF(G29&gt;H29,F29,I29)</f>
-        <v>Francia</v>
+        <v>Argentina</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>2</v>
@@ -6433,24 +6433,24 @@
         <v>209</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>210</v>
       </c>
       <c r="F34" s="0" t="str">
         <f aca="false">IF(G31&gt;H31,F31,I31)</f>
-        <v>Brasil</v>
+        <v>España</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="0" t="str">
         <f aca="false">IF(G32&gt;H32,F32,I32)</f>
-        <v>España</v>
+        <v>Francia</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>211</v>
@@ -6467,7 +6467,7 @@
         <v>213</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>214</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="I35" s="0" t="str">
         <f aca="false">IF(G34&gt;H34,I34,F34)</f>
-        <v>Brasil</v>
+        <v>Francia</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>215</v>
@@ -6501,14 +6501,14 @@
         <v>217</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>218</v>
       </c>
       <c r="F36" s="0" t="str">
         <f aca="false">IF(G33&gt;H33,F33,I33)</f>
-        <v>Francia</v>
+        <v>Argentina</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>1</v>

--- a/entregables/QUINIELA_2026_JAVIER_FINAL.xlsx
+++ b/entregables/QUINIELA_2026_JAVIER_FINAL.xlsx
@@ -382,10 +382,139 @@
     <t xml:space="preserve">Dieciseisavos</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2B</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-06-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Ángeles</t>
+    <t xml:space="preserve">Atlanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_ABCDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva York</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_CDFGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Francisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad de México</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_CEFHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_EHIJK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filadelfia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_BEFIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_AEHIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vancouver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monterrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_EFGIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miami</t>
   </si>
   <si>
     <t xml:space="preserve">1J</t>
@@ -394,10 +523,16 @@
     <t xml:space="preserve">2H</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas</t>
+    <t xml:space="preserve">Seattle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3_DEIJL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kansas City</t>
   </si>
   <si>
     <t xml:space="preserve">2D</t>
@@ -406,162 +541,30 @@
     <t xml:space="preserve">2G</t>
   </si>
   <si>
-    <t xml:space="preserve">Filadelfia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_DEIJL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_AEHIJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Francisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_EHIJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciudad de México</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_CEFHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monterrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vancouver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_EFGIJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva York</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_CDFGH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atlanta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seattle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_ABCDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kansas City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3_BEFIJ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Octavos</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-04</t>
   </si>
   <si>
+    <t xml:space="preserve">W74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W77</t>
+  </si>
+  <si>
     <t xml:space="preserve">W73</t>
   </si>
   <si>
-    <t xml:space="preserve">W74</t>
-  </si>
-  <si>
     <t xml:space="preserve">W75</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">W76</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W77</t>
-  </si>
-  <si>
     <t xml:space="preserve">W78</t>
   </si>
   <si>
@@ -574,66 +577,63 @@
     <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
+    <t xml:space="preserve">W83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W84</t>
+  </si>
+  <si>
     <t xml:space="preserve">W81</t>
   </si>
   <si>
     <t xml:space="preserve">W82</t>
   </si>
   <si>
-    <t xml:space="preserve">W83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W84</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
+    <t xml:space="preserve">W86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W88</t>
+  </si>
+  <si>
     <t xml:space="preserve">W85</t>
   </si>
   <si>
-    <t xml:space="preserve">W86</t>
-  </si>
-  <si>
     <t xml:space="preserve">W87</t>
   </si>
   <si>
-    <t xml:space="preserve">W88</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cuartos</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W92</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
-    <t xml:space="preserve">W89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miami</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">W95</t>
   </si>
   <si>
@@ -643,16 +643,16 @@
     <t xml:space="preserve">Semifinal</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W98</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
   </si>
   <si>
     <t xml:space="preserve">W99</t>
@@ -5461,18 +5461,18 @@
         <v>121</v>
       </c>
       <c r="F5" s="0" t="str">
-        <f aca="false">Grupos!$R$87</f>
-        <v>Argentina</v>
+        <f aca="false">Grupos!$R$7</f>
+        <v>Corea del Sur</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="0" t="str">
-        <f aca="false">Grupos!$R$70</f>
-        <v>Uruguay</v>
+        <f aca="false">Grupos!$R$16</f>
+        <v>Suiza</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>122</v>
@@ -5495,18 +5495,17 @@
         <v>125</v>
       </c>
       <c r="F6" s="0" t="str">
-        <f aca="false">Grupos!$R$34</f>
-        <v>Australia</v>
+        <f aca="false">Grupos!$R$42</f>
+        <v>Alemania</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="0" t="str">
-        <f aca="false">Grupos!$R$61</f>
-        <v>Irán</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>126</v>
@@ -5529,17 +5528,18 @@
         <v>128</v>
       </c>
       <c r="F7" s="0" t="str">
-        <f aca="false">Grupos!$R$96</f>
-        <v>Portugal</v>
+        <f aca="false">Grupos!$R$51</f>
+        <v>Holanda</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>95</v>
+        <v>1</v>
+      </c>
+      <c r="I7" s="0" t="str">
+        <f aca="false">Grupos!$R$25</f>
+        <v>Marruecos</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>129</v>
@@ -5553,29 +5553,30 @@
         <v>118</v>
       </c>
       <c r="C8" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="E8" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="F8" s="0" t="str">
+        <f aca="false">Grupos!$R$24</f>
+        <v>Brasil</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="str">
+        <f aca="false">Grupos!$R$52</f>
+        <v>Japón</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="F8" s="0" t="str">
-        <f aca="false">Grupos!$R$60</f>
-        <v>Bélgica</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5586,7 +5587,7 @@
         <v>118</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>134</v>
@@ -5595,18 +5596,17 @@
         <v>135</v>
       </c>
       <c r="F9" s="0" t="str">
-        <f aca="false">Grupos!$R$24</f>
-        <v>Brasil</v>
+        <f aca="false">Grupos!$R$78</f>
+        <v>Francia</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="0" t="str">
-        <f aca="false">Grupos!$R$52</f>
-        <v>Japón</v>
+      <c r="I9" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>136</v>
@@ -5620,13 +5620,13 @@
         <v>118</v>
       </c>
       <c r="C10" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="E10" s="0" t="s">
         <v>138</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>139</v>
       </c>
       <c r="F10" s="0" t="str">
         <f aca="false">Grupos!$R$43</f>
@@ -5643,7 +5643,7 @@
         <v>Noruega</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5654,29 +5654,29 @@
         <v>118</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="F11" s="0" t="str">
+        <f aca="false">Grupos!$R$6</f>
+        <v>México</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="F11" s="0" t="str">
-        <f aca="false">Grupos!$R$105</f>
-        <v>Inglaterra</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,7 +5687,7 @@
         <v>118</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>144</v>
@@ -5696,8 +5696,8 @@
         <v>145</v>
       </c>
       <c r="F12" s="0" t="str">
-        <f aca="false">Grupos!$R$6</f>
-        <v>México</v>
+        <f aca="false">Grupos!$R$105</f>
+        <v>Inglaterra</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>2</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>146</v>
@@ -5720,30 +5720,29 @@
         <v>118</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F13" s="0" t="str">
-        <f aca="false">Grupos!$R$69</f>
-        <v>España</v>
+        <f aca="false">Grupos!$R$33</f>
+        <v>Estados Unidos</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="0" t="str">
-        <f aca="false">Grupos!$R$88</f>
-        <v>Argelia</v>
+      <c r="I13" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5754,30 +5753,29 @@
         <v>118</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F14" s="0" t="str">
-        <f aca="false">Grupos!$R$7</f>
-        <v>Corea del Sur</v>
+        <f aca="false">Grupos!$R$60</f>
+        <v>Bélgica</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="0" t="str">
-        <f aca="false">Grupos!$R$16</f>
-        <v>Suiza</v>
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5788,17 +5786,17 @@
         <v>118</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F15" s="0" t="str">
-        <f aca="false">Grupos!$R$51</f>
-        <v>Holanda</v>
+        <f aca="false">Grupos!$R$97</f>
+        <v>Colombia</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>2</v>
@@ -5807,11 +5805,11 @@
         <v>1</v>
       </c>
       <c r="I15" s="0" t="str">
-        <f aca="false">Grupos!$R$25</f>
-        <v>Marruecos</v>
+        <f aca="false">Grupos!$R$106</f>
+        <v>Croacia</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5822,29 +5820,30 @@
         <v>118</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F16" s="0" t="str">
-        <f aca="false">Grupos!$R$15</f>
-        <v>Canadá</v>
+        <f aca="false">Grupos!$R$69</f>
+        <v>España</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>81</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="0" t="str">
+        <f aca="false">Grupos!$R$88</f>
+        <v>Argelia</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5855,29 +5854,29 @@
         <v>118</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F17" s="0" t="str">
-        <f aca="false">Grupos!$R$78</f>
-        <v>Francia</v>
+        <f aca="false">Grupos!$R$15</f>
+        <v>Canadá</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5888,30 +5887,30 @@
         <v>118</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F18" s="0" t="str">
-        <f aca="false">Grupos!$R$97</f>
-        <v>Colombia</v>
+        <f aca="false">Grupos!$R$87</f>
+        <v>Argentina</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0" t="str">
-        <f aca="false">Grupos!$R$106</f>
-        <v>Croacia</v>
+        <f aca="false">Grupos!$R$70</f>
+        <v>Uruguay</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5922,29 +5921,29 @@
         <v>118</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F19" s="0" t="str">
-        <f aca="false">Grupos!$R$42</f>
-        <v>Alemania</v>
+        <f aca="false">Grupos!$R$96</f>
+        <v>Portugal</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5955,29 +5954,30 @@
         <v>118</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F20" s="0" t="str">
-        <f aca="false">Grupos!$R$33</f>
-        <v>Estados Unidos</v>
+        <f aca="false">Grupos!$R$34</f>
+        <v>Australia</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>56</v>
+        <v>2</v>
+      </c>
+      <c r="I20" s="0" t="str">
+        <f aca="false">Grupos!$R$61</f>
+        <v>Irán</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5985,33 +5985,33 @@
         <v>89</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F21" s="0" t="str">
-        <f aca="false">IF(G5&gt;H5,F5,I5)</f>
-        <v>Argentina</v>
+        <f aca="false">IF(G6&gt;H6,F6,I6)</f>
+        <v>Alemania</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" s="0" t="str">
-        <f aca="false">IF(G6&gt;H6,F6,I6)</f>
-        <v>Irán</v>
+        <f aca="false">IF(G9&gt;H9,F9,I9)</f>
+        <v>Francia</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,33 +6019,33 @@
         <v>90</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>127</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F22" s="0" t="str">
+        <f aca="false">IF(G5&gt;H5,F5,I5)</f>
+        <v>Suiza</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="0" t="str">
         <f aca="false">IF(G7&gt;H7,F7,I7)</f>
-        <v>Portugal</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="0" t="str">
-        <f aca="false">IF(G8&gt;H8,F8,I8)</f>
-        <v>Bélgica</v>
+        <v>Holanda</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6053,19 +6053,19 @@
         <v>91</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F23" s="0" t="str">
-        <f aca="false">IF(G9&gt;H9,F9,I9)</f>
+        <f aca="false">IF(G8&gt;H8,F8,I8)</f>
         <v>Brasil</v>
       </c>
       <c r="G23" s="4" t="n">
@@ -6079,7 +6079,7 @@
         <v>Ecuador</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6087,33 +6087,33 @@
         <v>92</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="0" t="str">
         <f aca="false">IF(G11&gt;H11,F11,I11)</f>
-        <v>Inglaterra</v>
+        <v>México</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="0" t="str">
         <f aca="false">IF(G12&gt;H12,F12,I12)</f>
-        <v>México</v>
+        <v>Inglaterra</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6121,33 +6121,33 @@
         <v>93</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F25" s="0" t="str">
-        <f aca="false">IF(G13&gt;H13,F13,I13)</f>
+        <f aca="false">IF(G15&gt;H15,F15,I15)</f>
+        <v>Colombia</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="0" t="str">
+        <f aca="false">IF(G16&gt;H16,F16,I16)</f>
         <v>España</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="0" t="str">
-        <f aca="false">IF(G14&gt;H14,F14,I14)</f>
-        <v>Suiza</v>
-      </c>
       <c r="J25" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6155,33 +6155,33 @@
         <v>94</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F26" s="0" t="str">
-        <f aca="false">IF(G15&gt;H15,F15,I15)</f>
-        <v>Holanda</v>
+        <f aca="false">IF(G13&gt;H13,F13,I13)</f>
+        <v>Estados Unidos</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="0" t="str">
-        <f aca="false">IF(G16&gt;H16,F16,I16)</f>
-        <v>Canadá</v>
+        <f aca="false">IF(G14&gt;H14,F14,I14)</f>
+        <v>Bélgica</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6189,33 +6189,33 @@
         <v>95</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F27" s="0" t="str">
-        <f aca="false">IF(G17&gt;H17,F17,I17)</f>
-        <v>Francia</v>
+        <f aca="false">IF(G18&gt;H18,F18,I18)</f>
+        <v>Argentina</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0" t="str">
-        <f aca="false">IF(G18&gt;H18,F18,I18)</f>
-        <v>Colombia</v>
+        <f aca="false">IF(G20&gt;H20,F20,I20)</f>
+        <v>Irán</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6223,33 +6223,33 @@
         <v>96</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F28" s="0" t="str">
+        <f aca="false">IF(G17&gt;H17,F17,I17)</f>
+        <v>Canadá</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="0" t="str">
         <f aca="false">IF(G19&gt;H19,F19,I19)</f>
-        <v>Alemania</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="0" t="str">
-        <f aca="false">IF(G20&gt;H20,F20,I20)</f>
-        <v>Estados Unidos</v>
+        <v>Portugal</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6257,20 +6257,20 @@
         <v>97</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F29" s="0" t="str">
         <f aca="false">IF(G21&gt;H21,F21,I21)</f>
-        <v>Argentina</v>
+        <v>Francia</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>2</v>
@@ -6280,10 +6280,10 @@
       </c>
       <c r="I29" s="0" t="str">
         <f aca="false">IF(G22&gt;H22,F22,I22)</f>
-        <v>Portugal</v>
+        <v>Holanda</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,33 +6291,33 @@
         <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="0" t="str">
-        <f aca="false">IF(G23&gt;H23,F23,I23)</f>
-        <v>Brasil</v>
+        <f aca="false">IF(G25&gt;H25,F25,I25)</f>
+        <v>España</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0" t="str">
-        <f aca="false">IF(G24&gt;H24,F24,I24)</f>
-        <v>Inglaterra</v>
+        <f aca="false">IF(G26&gt;H26,F26,I26)</f>
+        <v>Estados Unidos</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6325,30 +6325,30 @@
         <v>99</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>200</v>
       </c>
       <c r="F31" s="0" t="str">
-        <f aca="false">IF(G25&gt;H25,F25,I25)</f>
-        <v>España</v>
+        <f aca="false">IF(G23&gt;H23,F23,I23)</f>
+        <v>Brasil</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="0" t="str">
-        <f aca="false">IF(G26&gt;H26,F26,I26)</f>
-        <v>Holanda</v>
+        <f aca="false">IF(G24&gt;H24,F24,I24)</f>
+        <v>Inglaterra</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>201</v>
@@ -6359,20 +6359,20 @@
         <v>100</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>202</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>203</v>
       </c>
       <c r="F32" s="0" t="str">
         <f aca="false">IF(G27&gt;H27,F27,I27)</f>
-        <v>Francia</v>
+        <v>Argentina</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>2</v>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I32" s="0" t="str">
         <f aca="false">IF(G28&gt;H28,F28,I28)</f>
-        <v>Alemania</v>
+        <v>Portugal</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>204</v>
@@ -6399,24 +6399,24 @@
         <v>206</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>207</v>
       </c>
       <c r="F33" s="0" t="str">
         <f aca="false">IF(G29&gt;H29,F29,I29)</f>
-        <v>Argentina</v>
+        <v>Francia</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="0" t="str">
         <f aca="false">IF(G30&gt;H30,F30,I30)</f>
-        <v>Inglaterra</v>
+        <v>España</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>208</v>
@@ -6440,17 +6440,17 @@
       </c>
       <c r="F34" s="0" t="str">
         <f aca="false">IF(G31&gt;H31,F31,I31)</f>
-        <v>España</v>
+        <v>Inglaterra</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="0" t="str">
         <f aca="false">IF(G32&gt;H32,F32,I32)</f>
-        <v>Francia</v>
+        <v>Argentina</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>211</v>
@@ -6467,24 +6467,24 @@
         <v>213</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>214</v>
       </c>
       <c r="F35" s="0" t="str">
         <f aca="false">IF(G33&gt;H33,I33,F33)</f>
-        <v>Inglaterra</v>
+        <v>Francia</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" s="0" t="str">
         <f aca="false">IF(G34&gt;H34,I34,F34)</f>
-        <v>Francia</v>
+        <v>Inglaterra</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>215</v>
@@ -6501,24 +6501,24 @@
         <v>217</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>218</v>
       </c>
       <c r="F36" s="0" t="str">
         <f aca="false">IF(G33&gt;H33,F33,I33)</f>
-        <v>Argentina</v>
+        <v>España</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="0" t="str">
         <f aca="false">IF(G34&gt;H34,F34,I34)</f>
-        <v>España</v>
+        <v>Argentina</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>219</v>
